--- a/Result/profitability/6225.xlsx
+++ b/Result/profitability/6225.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,16 +669,16 @@
         <v>0.03</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.03124999999999999</v>
+        <v>-0.01875</v>
       </c>
       <c r="N2" t="n">
-        <v>28.96625</v>
+        <v>33.42625</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
       </c>
       <c r="P2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
@@ -687,7 +687,7 @@
         <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>0.05</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.015</v>
+        <v>-0.008749999999999994</v>
       </c>
       <c r="N3" t="n">
-        <v>28.86625</v>
+        <v>33.71125</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,13 +899,13 @@
         <v>0.01</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.009999999999999995</v>
+        <v>0.01125</v>
       </c>
       <c r="N4" t="n">
-        <v>29.46875</v>
+        <v>33.94875</v>
       </c>
       <c r="O4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>-0.86</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.09874999999999999</v>
+        <v>-0.105</v>
       </c>
       <c r="N5" t="n">
-        <v>28.5275</v>
+        <v>30.43</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>-0.6</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.1825</v>
+        <v>-0.16625</v>
       </c>
       <c r="N6" t="n">
-        <v>25.6575</v>
+        <v>25.7525</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>-0.41</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.22</v>
+        <v>-0.23375</v>
       </c>
       <c r="N7" t="n">
-        <v>20.59375</v>
+        <v>21.9575</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>0.19</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.2125</v>
+        <v>-0.19625</v>
       </c>
       <c r="N8" t="n">
-        <v>18.4475</v>
+        <v>23.61375</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -9834,6 +9834,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>6225</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>21</v>
+      </c>
+      <c r="D75" t="n">
+        <v>9</v>
+      </c>
+      <c r="E75" t="n">
+        <v>11</v>
+      </c>
+      <c r="F75" t="n">
+        <v>54.59</v>
+      </c>
+      <c r="G75" t="n">
+        <v>1</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>2.72%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>0</v>
+      </c>
+      <c r="J75" t="n">
+        <v>1</v>
+      </c>
+      <c r="K75" t="n">
+        <v>1</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="M75" t="n">
+        <v>-0.03249999999999999</v>
+      </c>
+      <c r="N75" t="n">
+        <v>32.2775</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>1</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-1.181818181818182</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>41.33000000000001</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>3.116892911010559</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-0.7142857142857143</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>15.22000000000001</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.3865887731775466</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS衰退 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
